--- a/artfynd/A 569-2023 artfynd.xlsx
+++ b/artfynd/A 569-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 569-2023 artfynd.xlsx
+++ b/artfynd/A 569-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3034,6 +3034,2216 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128305487</v>
+      </c>
+      <c r="B23" t="n">
+        <v>109297</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>704285</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6360090</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Pansartall, levande, med flagnande bark och en del insektshål.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128305385</v>
+      </c>
+      <c r="B24" t="n">
+        <v>106766</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>704296</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6359878</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128305390</v>
+      </c>
+      <c r="B25" t="n">
+        <v>106766</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>704316</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6359869</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128305478</v>
+      </c>
+      <c r="B26" t="n">
+        <v>106766</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>704346</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6360116</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128305426</v>
+      </c>
+      <c r="B27" t="n">
+        <v>107355</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>704548</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6359959</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128305377</v>
+      </c>
+      <c r="B28" t="n">
+        <v>109297</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>704248</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6359861</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128305421</v>
+      </c>
+      <c r="B29" t="n">
+        <v>103926</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>704541</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6359927</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128305424</v>
+      </c>
+      <c r="B30" t="n">
+        <v>107355</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>704541</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6359927</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128305408</v>
+      </c>
+      <c r="B31" t="n">
+        <v>106766</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>704448</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6359872</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128305378</v>
+      </c>
+      <c r="B32" t="n">
+        <v>106766</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>704248</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6359861</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128305410</v>
+      </c>
+      <c r="B33" t="n">
+        <v>103926</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>704471</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6359883</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128305384</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98498</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>704296</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6359878</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128305411</v>
+      </c>
+      <c r="B35" t="n">
+        <v>106766</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>704471</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6359883</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128305475</v>
+      </c>
+      <c r="B36" t="n">
+        <v>106766</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>704379</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6360148</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128305423</v>
+      </c>
+      <c r="B37" t="n">
+        <v>106766</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>704541</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6359927</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128305413</v>
+      </c>
+      <c r="B38" t="n">
+        <v>103926</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>704517</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6359895</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128305407</v>
+      </c>
+      <c r="B39" t="n">
+        <v>103926</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>704448</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6359872</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128305483</v>
+      </c>
+      <c r="B40" t="n">
+        <v>106766</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>704298</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6360088</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128305381</v>
+      </c>
+      <c r="B41" t="n">
+        <v>107355</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>704287</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6359876</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128305490</v>
+      </c>
+      <c r="B42" t="n">
+        <v>109297</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>704264</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6360097</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128305414</v>
+      </c>
+      <c r="B43" t="n">
+        <v>106766</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>704517</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6359895</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 569-2023 artfynd.xlsx
+++ b/artfynd/A 569-2023 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>128305487</v>
       </c>
       <c r="B23" t="n">
-        <v>109297</v>
+        <v>109305</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,10 +3152,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128305385</v>
+        <v>128305390</v>
       </c>
       <c r="B24" t="n">
-        <v>106766</v>
+        <v>106774</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>704296</v>
+        <v>704316</v>
       </c>
       <c r="R24" t="n">
-        <v>6359878</v>
+        <v>6359869</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3254,10 +3254,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128305390</v>
+        <v>128305385</v>
       </c>
       <c r="B25" t="n">
-        <v>106766</v>
+        <v>106774</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>704316</v>
+        <v>704296</v>
       </c>
       <c r="R25" t="n">
-        <v>6359869</v>
+        <v>6359878</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128305478</v>
+        <v>128305377</v>
       </c>
       <c r="B26" t="n">
-        <v>106766</v>
+        <v>109305</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3367,16 +3367,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3384,17 +3384,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>704346</v>
+        <v>704248</v>
       </c>
       <c r="R26" t="n">
-        <v>6360116</v>
+        <v>6359861</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3461,7 +3470,7 @@
         <v>128305426</v>
       </c>
       <c r="B27" t="n">
-        <v>107355</v>
+        <v>107363</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,10 +3578,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128305377</v>
+        <v>128305478</v>
       </c>
       <c r="B28" t="n">
-        <v>109297</v>
+        <v>106774</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3580,16 +3589,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3597,26 +3606,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>704248</v>
+        <v>704346</v>
       </c>
       <c r="R28" t="n">
-        <v>6359861</v>
+        <v>6360116</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3683,7 +3683,7 @@
         <v>128305421</v>
       </c>
       <c r="B29" t="n">
-        <v>103926</v>
+        <v>103934</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>128305424</v>
       </c>
       <c r="B30" t="n">
-        <v>107355</v>
+        <v>107363</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>128305408</v>
       </c>
       <c r="B31" t="n">
-        <v>106766</v>
+        <v>106774</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3995,10 +3995,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128305378</v>
+        <v>128305410</v>
       </c>
       <c r="B32" t="n">
-        <v>106766</v>
+        <v>103934</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4006,21 +4006,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4030,10 +4030,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>704248</v>
+        <v>704471</v>
       </c>
       <c r="R32" t="n">
-        <v>6359861</v>
+        <v>6359883</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4097,10 +4097,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128305410</v>
+        <v>128305378</v>
       </c>
       <c r="B33" t="n">
-        <v>103926</v>
+        <v>106774</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,21 +4108,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>704471</v>
+        <v>704248</v>
       </c>
       <c r="R33" t="n">
-        <v>6359883</v>
+        <v>6359861</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4202,7 +4202,7 @@
         <v>128305384</v>
       </c>
       <c r="B34" t="n">
-        <v>98498</v>
+        <v>98506</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>128305411</v>
       </c>
       <c r="B35" t="n">
-        <v>106766</v>
+        <v>106774</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>128305475</v>
       </c>
       <c r="B36" t="n">
-        <v>106766</v>
+        <v>106774</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4514,10 +4514,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128305423</v>
+        <v>128305413</v>
       </c>
       <c r="B37" t="n">
-        <v>106766</v>
+        <v>103934</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4525,21 +4525,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4549,10 +4549,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>704541</v>
+        <v>704517</v>
       </c>
       <c r="R37" t="n">
-        <v>6359927</v>
+        <v>6359895</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128305413</v>
+        <v>128305423</v>
       </c>
       <c r="B38" t="n">
-        <v>103926</v>
+        <v>106774</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4627,21 +4627,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4651,10 +4651,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>704517</v>
+        <v>704541</v>
       </c>
       <c r="R38" t="n">
-        <v>6359895</v>
+        <v>6359927</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4721,7 +4721,7 @@
         <v>128305407</v>
       </c>
       <c r="B39" t="n">
-        <v>103926</v>
+        <v>103934</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4820,10 +4820,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128305483</v>
+        <v>128305381</v>
       </c>
       <c r="B40" t="n">
-        <v>106766</v>
+        <v>107363</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4831,31 +4831,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>704298</v>
+        <v>704287</v>
       </c>
       <c r="R40" t="n">
-        <v>6360088</v>
+        <v>6359876</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4931,10 +4931,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128305381</v>
+        <v>128305483</v>
       </c>
       <c r="B41" t="n">
-        <v>107355</v>
+        <v>106774</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4942,31 +4942,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4975,10 +4975,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>704287</v>
+        <v>704298</v>
       </c>
       <c r="R41" t="n">
-        <v>6359876</v>
+        <v>6360088</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5045,7 +5045,7 @@
         <v>128305490</v>
       </c>
       <c r="B42" t="n">
-        <v>109297</v>
+        <v>109305</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>128305414</v>
       </c>
       <c r="B43" t="n">
-        <v>106766</v>
+        <v>106774</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 569-2023 artfynd.xlsx
+++ b/artfynd/A 569-2023 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>128305487</v>
       </c>
       <c r="B23" t="n">
-        <v>109305</v>
+        <v>109398</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,10 +3152,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128305390</v>
+        <v>128305385</v>
       </c>
       <c r="B24" t="n">
-        <v>106774</v>
+        <v>106867</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>704316</v>
+        <v>704296</v>
       </c>
       <c r="R24" t="n">
-        <v>6359869</v>
+        <v>6359878</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3254,10 +3254,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128305385</v>
+        <v>128305390</v>
       </c>
       <c r="B25" t="n">
-        <v>106774</v>
+        <v>106867</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>704296</v>
+        <v>704316</v>
       </c>
       <c r="R25" t="n">
-        <v>6359878</v>
+        <v>6359869</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128305377</v>
+        <v>128305478</v>
       </c>
       <c r="B26" t="n">
-        <v>109305</v>
+        <v>106867</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3367,16 +3367,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3384,26 +3384,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>704248</v>
+        <v>704346</v>
       </c>
       <c r="R26" t="n">
-        <v>6359861</v>
+        <v>6360116</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3470,7 +3461,7 @@
         <v>128305426</v>
       </c>
       <c r="B27" t="n">
-        <v>107363</v>
+        <v>107456</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3578,10 +3569,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128305478</v>
+        <v>128305377</v>
       </c>
       <c r="B28" t="n">
-        <v>106774</v>
+        <v>109398</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3589,16 +3580,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3606,17 +3597,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>704346</v>
+        <v>704248</v>
       </c>
       <c r="R28" t="n">
-        <v>6360116</v>
+        <v>6359861</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3683,7 +3683,7 @@
         <v>128305421</v>
       </c>
       <c r="B29" t="n">
-        <v>103934</v>
+        <v>104027</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>128305424</v>
       </c>
       <c r="B30" t="n">
-        <v>107363</v>
+        <v>107456</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>128305408</v>
       </c>
       <c r="B31" t="n">
-        <v>106774</v>
+        <v>106867</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>128305410</v>
       </c>
       <c r="B32" t="n">
-        <v>103934</v>
+        <v>104027</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>128305378</v>
       </c>
       <c r="B33" t="n">
-        <v>106774</v>
+        <v>106867</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>128305384</v>
       </c>
       <c r="B34" t="n">
-        <v>98506</v>
+        <v>98599</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>128305411</v>
       </c>
       <c r="B35" t="n">
-        <v>106774</v>
+        <v>106867</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>128305475</v>
       </c>
       <c r="B36" t="n">
-        <v>106774</v>
+        <v>106867</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4514,10 +4514,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128305413</v>
+        <v>128305423</v>
       </c>
       <c r="B37" t="n">
-        <v>103934</v>
+        <v>106867</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4525,21 +4525,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4549,10 +4549,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>704517</v>
+        <v>704541</v>
       </c>
       <c r="R37" t="n">
-        <v>6359895</v>
+        <v>6359927</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128305423</v>
+        <v>128305413</v>
       </c>
       <c r="B38" t="n">
-        <v>106774</v>
+        <v>104027</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4627,21 +4627,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4651,10 +4651,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>704541</v>
+        <v>704517</v>
       </c>
       <c r="R38" t="n">
-        <v>6359927</v>
+        <v>6359895</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4721,7 +4721,7 @@
         <v>128305407</v>
       </c>
       <c r="B39" t="n">
-        <v>103934</v>
+        <v>104027</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4820,10 +4820,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128305381</v>
+        <v>128305483</v>
       </c>
       <c r="B40" t="n">
-        <v>107363</v>
+        <v>106867</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4831,31 +4831,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>704287</v>
+        <v>704298</v>
       </c>
       <c r="R40" t="n">
-        <v>6359876</v>
+        <v>6360088</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4931,10 +4931,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128305483</v>
+        <v>128305381</v>
       </c>
       <c r="B41" t="n">
-        <v>106774</v>
+        <v>107456</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4942,31 +4942,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4975,10 +4975,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>704298</v>
+        <v>704287</v>
       </c>
       <c r="R41" t="n">
-        <v>6360088</v>
+        <v>6359876</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5045,7 +5045,7 @@
         <v>128305490</v>
       </c>
       <c r="B42" t="n">
-        <v>109305</v>
+        <v>109398</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>128305414</v>
       </c>
       <c r="B43" t="n">
-        <v>106774</v>
+        <v>106867</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 569-2023 artfynd.xlsx
+++ b/artfynd/A 569-2023 artfynd.xlsx
@@ -3356,10 +3356,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128305478</v>
+        <v>128305426</v>
       </c>
       <c r="B26" t="n">
-        <v>106867</v>
+        <v>107456</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3367,34 +3367,43 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>704346</v>
+        <v>704548</v>
       </c>
       <c r="R26" t="n">
-        <v>6360116</v>
+        <v>6359959</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3458,10 +3467,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128305426</v>
+        <v>128305377</v>
       </c>
       <c r="B27" t="n">
-        <v>107456</v>
+        <v>109398</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3469,26 +3478,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3502,10 +3511,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>704548</v>
+        <v>704248</v>
       </c>
       <c r="R27" t="n">
-        <v>6359959</v>
+        <v>6359861</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3569,10 +3578,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128305377</v>
+        <v>128305478</v>
       </c>
       <c r="B28" t="n">
-        <v>109398</v>
+        <v>106867</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3580,16 +3589,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3597,26 +3606,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>704248</v>
+        <v>704346</v>
       </c>
       <c r="R28" t="n">
-        <v>6359861</v>
+        <v>6360116</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4514,10 +4514,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128305423</v>
+        <v>128305413</v>
       </c>
       <c r="B37" t="n">
-        <v>106867</v>
+        <v>104027</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4525,21 +4525,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4549,10 +4549,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>704541</v>
+        <v>704517</v>
       </c>
       <c r="R37" t="n">
-        <v>6359927</v>
+        <v>6359895</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128305413</v>
+        <v>128305423</v>
       </c>
       <c r="B38" t="n">
-        <v>104027</v>
+        <v>106867</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4627,21 +4627,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4651,10 +4651,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>704517</v>
+        <v>704541</v>
       </c>
       <c r="R38" t="n">
-        <v>6359895</v>
+        <v>6359927</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5042,10 +5042,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128305490</v>
+        <v>128305414</v>
       </c>
       <c r="B42" t="n">
-        <v>109398</v>
+        <v>106867</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5053,16 +5053,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>704264</v>
+        <v>704517</v>
       </c>
       <c r="R42" t="n">
-        <v>6360097</v>
+        <v>6359895</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5144,10 +5144,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128305414</v>
+        <v>128305490</v>
       </c>
       <c r="B43" t="n">
-        <v>106867</v>
+        <v>109398</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5155,16 +5155,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>704517</v>
+        <v>704264</v>
       </c>
       <c r="R43" t="n">
-        <v>6359895</v>
+        <v>6360097</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 569-2023 artfynd.xlsx
+++ b/artfynd/A 569-2023 artfynd.xlsx
@@ -5042,10 +5042,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128305414</v>
+        <v>128305490</v>
       </c>
       <c r="B42" t="n">
-        <v>106867</v>
+        <v>109398</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5053,16 +5053,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>704517</v>
+        <v>704264</v>
       </c>
       <c r="R42" t="n">
-        <v>6359895</v>
+        <v>6360097</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5144,10 +5144,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128305490</v>
+        <v>128305414</v>
       </c>
       <c r="B43" t="n">
-        <v>109398</v>
+        <v>106867</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5155,16 +5155,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>704264</v>
+        <v>704517</v>
       </c>
       <c r="R43" t="n">
-        <v>6360097</v>
+        <v>6359895</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 569-2023 artfynd.xlsx
+++ b/artfynd/A 569-2023 artfynd.xlsx
@@ -3356,10 +3356,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128305426</v>
+        <v>128305377</v>
       </c>
       <c r="B26" t="n">
-        <v>107456</v>
+        <v>109398</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3367,26 +3367,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>704548</v>
+        <v>704248</v>
       </c>
       <c r="R26" t="n">
-        <v>6359959</v>
+        <v>6359861</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128305377</v>
+        <v>128305478</v>
       </c>
       <c r="B27" t="n">
-        <v>109398</v>
+        <v>106867</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3478,16 +3478,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3495,26 +3495,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>704248</v>
+        <v>704346</v>
       </c>
       <c r="R27" t="n">
-        <v>6359861</v>
+        <v>6360116</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3578,10 +3569,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128305478</v>
+        <v>128305426</v>
       </c>
       <c r="B28" t="n">
-        <v>106867</v>
+        <v>107456</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3589,34 +3580,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>704346</v>
+        <v>704548</v>
       </c>
       <c r="R28" t="n">
-        <v>6360116</v>
+        <v>6359959</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>

--- a/artfynd/A 569-2023 artfynd.xlsx
+++ b/artfynd/A 569-2023 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>128305487</v>
       </c>
       <c r="B23" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>128305385</v>
       </c>
       <c r="B24" t="n">
-        <v>106867</v>
+        <v>106890</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>128305390</v>
       </c>
       <c r="B25" t="n">
-        <v>106867</v>
+        <v>106890</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>128305377</v>
       </c>
       <c r="B26" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>128305478</v>
       </c>
       <c r="B27" t="n">
-        <v>106867</v>
+        <v>106890</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>128305426</v>
       </c>
       <c r="B28" t="n">
-        <v>107456</v>
+        <v>107479</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>128305421</v>
       </c>
       <c r="B29" t="n">
-        <v>104027</v>
+        <v>104048</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>128305424</v>
       </c>
       <c r="B30" t="n">
-        <v>107456</v>
+        <v>107479</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>128305408</v>
       </c>
       <c r="B31" t="n">
-        <v>106867</v>
+        <v>106890</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3995,10 +3995,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128305410</v>
+        <v>128305378</v>
       </c>
       <c r="B32" t="n">
-        <v>104027</v>
+        <v>106890</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4006,21 +4006,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4030,10 +4030,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>704471</v>
+        <v>704248</v>
       </c>
       <c r="R32" t="n">
-        <v>6359883</v>
+        <v>6359861</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4097,10 +4097,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128305378</v>
+        <v>128305410</v>
       </c>
       <c r="B33" t="n">
-        <v>106867</v>
+        <v>104048</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,21 +4108,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>704248</v>
+        <v>704471</v>
       </c>
       <c r="R33" t="n">
-        <v>6359861</v>
+        <v>6359883</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4202,7 +4202,7 @@
         <v>128305384</v>
       </c>
       <c r="B34" t="n">
-        <v>98599</v>
+        <v>98613</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>128305411</v>
       </c>
       <c r="B35" t="n">
-        <v>106867</v>
+        <v>106890</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>128305475</v>
       </c>
       <c r="B36" t="n">
-        <v>106867</v>
+        <v>106890</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>128305413</v>
       </c>
       <c r="B37" t="n">
-        <v>104027</v>
+        <v>104048</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>128305423</v>
       </c>
       <c r="B38" t="n">
-        <v>106867</v>
+        <v>106890</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>128305407</v>
       </c>
       <c r="B39" t="n">
-        <v>104027</v>
+        <v>104048</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4820,10 +4820,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128305483</v>
+        <v>128305381</v>
       </c>
       <c r="B40" t="n">
-        <v>106867</v>
+        <v>107479</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4831,31 +4831,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>704298</v>
+        <v>704287</v>
       </c>
       <c r="R40" t="n">
-        <v>6360088</v>
+        <v>6359876</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4931,10 +4931,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128305381</v>
+        <v>128305483</v>
       </c>
       <c r="B41" t="n">
-        <v>107456</v>
+        <v>106890</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4942,31 +4942,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4975,10 +4975,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>704287</v>
+        <v>704298</v>
       </c>
       <c r="R41" t="n">
-        <v>6359876</v>
+        <v>6360088</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5045,7 +5045,7 @@
         <v>128305490</v>
       </c>
       <c r="B42" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>128305414</v>
       </c>
       <c r="B43" t="n">
-        <v>106867</v>
+        <v>106890</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 569-2023 artfynd.xlsx
+++ b/artfynd/A 569-2023 artfynd.xlsx
@@ -3356,10 +3356,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128305377</v>
+        <v>128305426</v>
       </c>
       <c r="B26" t="n">
-        <v>109422</v>
+        <v>107479</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3367,26 +3367,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>704248</v>
+        <v>704548</v>
       </c>
       <c r="R26" t="n">
-        <v>6359861</v>
+        <v>6359959</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128305478</v>
+        <v>128305377</v>
       </c>
       <c r="B27" t="n">
-        <v>106890</v>
+        <v>109422</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3478,16 +3478,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3495,17 +3495,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>704346</v>
+        <v>704248</v>
       </c>
       <c r="R27" t="n">
-        <v>6360116</v>
+        <v>6359861</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3569,10 +3578,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128305426</v>
+        <v>128305478</v>
       </c>
       <c r="B28" t="n">
-        <v>107479</v>
+        <v>106890</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3580,43 +3589,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>704548</v>
+        <v>704346</v>
       </c>
       <c r="R28" t="n">
-        <v>6359959</v>
+        <v>6360116</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4514,10 +4514,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128305413</v>
+        <v>128305423</v>
       </c>
       <c r="B37" t="n">
-        <v>104048</v>
+        <v>106890</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4525,21 +4525,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4549,10 +4549,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>704517</v>
+        <v>704541</v>
       </c>
       <c r="R37" t="n">
-        <v>6359895</v>
+        <v>6359927</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128305423</v>
+        <v>128305413</v>
       </c>
       <c r="B38" t="n">
-        <v>106890</v>
+        <v>104048</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4627,21 +4627,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4651,10 +4651,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>704541</v>
+        <v>704517</v>
       </c>
       <c r="R38" t="n">
-        <v>6359927</v>
+        <v>6359895</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>

--- a/artfynd/A 569-2023 artfynd.xlsx
+++ b/artfynd/A 569-2023 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>128305487</v>
       </c>
       <c r="B23" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>128305385</v>
       </c>
       <c r="B24" t="n">
-        <v>106890</v>
+        <v>106902</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>128305390</v>
       </c>
       <c r="B25" t="n">
-        <v>106890</v>
+        <v>106902</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128305426</v>
+        <v>128305377</v>
       </c>
       <c r="B26" t="n">
-        <v>107479</v>
+        <v>109435</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3367,26 +3367,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>704548</v>
+        <v>704248</v>
       </c>
       <c r="R26" t="n">
-        <v>6359959</v>
+        <v>6359861</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128305377</v>
+        <v>128305478</v>
       </c>
       <c r="B27" t="n">
-        <v>109422</v>
+        <v>106902</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3478,16 +3478,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3495,26 +3495,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>704248</v>
+        <v>704346</v>
       </c>
       <c r="R27" t="n">
-        <v>6359861</v>
+        <v>6360116</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3578,10 +3569,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128305478</v>
+        <v>128305426</v>
       </c>
       <c r="B28" t="n">
-        <v>106890</v>
+        <v>107491</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3589,34 +3580,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>704346</v>
+        <v>704548</v>
       </c>
       <c r="R28" t="n">
-        <v>6360116</v>
+        <v>6359959</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3683,7 +3683,7 @@
         <v>128305421</v>
       </c>
       <c r="B29" t="n">
-        <v>104048</v>
+        <v>104060</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>128305424</v>
       </c>
       <c r="B30" t="n">
-        <v>107479</v>
+        <v>107491</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>128305408</v>
       </c>
       <c r="B31" t="n">
-        <v>106890</v>
+        <v>106902</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>128305378</v>
       </c>
       <c r="B32" t="n">
-        <v>106890</v>
+        <v>106902</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>128305410</v>
       </c>
       <c r="B33" t="n">
-        <v>104048</v>
+        <v>104060</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>128305384</v>
       </c>
       <c r="B34" t="n">
-        <v>98613</v>
+        <v>98616</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>128305411</v>
       </c>
       <c r="B35" t="n">
-        <v>106890</v>
+        <v>106902</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>128305475</v>
       </c>
       <c r="B36" t="n">
-        <v>106890</v>
+        <v>106902</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4514,10 +4514,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128305423</v>
+        <v>128305413</v>
       </c>
       <c r="B37" t="n">
-        <v>106890</v>
+        <v>104060</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4525,21 +4525,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4549,10 +4549,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>704541</v>
+        <v>704517</v>
       </c>
       <c r="R37" t="n">
-        <v>6359927</v>
+        <v>6359895</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128305413</v>
+        <v>128305423</v>
       </c>
       <c r="B38" t="n">
-        <v>104048</v>
+        <v>106902</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4627,21 +4627,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4651,10 +4651,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>704517</v>
+        <v>704541</v>
       </c>
       <c r="R38" t="n">
-        <v>6359895</v>
+        <v>6359927</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4721,7 +4721,7 @@
         <v>128305407</v>
       </c>
       <c r="B39" t="n">
-        <v>104048</v>
+        <v>104060</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>128305381</v>
       </c>
       <c r="B40" t="n">
-        <v>107479</v>
+        <v>107491</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>128305483</v>
       </c>
       <c r="B41" t="n">
-        <v>106890</v>
+        <v>106902</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>128305490</v>
       </c>
       <c r="B42" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>128305414</v>
       </c>
       <c r="B43" t="n">
-        <v>106890</v>
+        <v>106902</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 569-2023 artfynd.xlsx
+++ b/artfynd/A 569-2023 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>128305487</v>
       </c>
       <c r="B23" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>128305385</v>
       </c>
       <c r="B24" t="n">
-        <v>106902</v>
+        <v>106911</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>128305390</v>
       </c>
       <c r="B25" t="n">
-        <v>106902</v>
+        <v>106911</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128305377</v>
+        <v>128305426</v>
       </c>
       <c r="B26" t="n">
-        <v>109435</v>
+        <v>107500</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3367,26 +3367,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>704248</v>
+        <v>704548</v>
       </c>
       <c r="R26" t="n">
-        <v>6359861</v>
+        <v>6359959</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3470,7 +3470,7 @@
         <v>128305478</v>
       </c>
       <c r="B27" t="n">
-        <v>106902</v>
+        <v>106911</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,10 +3569,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128305426</v>
+        <v>128305377</v>
       </c>
       <c r="B28" t="n">
-        <v>107491</v>
+        <v>109444</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3580,26 +3580,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>704548</v>
+        <v>704248</v>
       </c>
       <c r="R28" t="n">
-        <v>6359959</v>
+        <v>6359861</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3683,7 +3683,7 @@
         <v>128305421</v>
       </c>
       <c r="B29" t="n">
-        <v>104060</v>
+        <v>104069</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>128305424</v>
       </c>
       <c r="B30" t="n">
-        <v>107491</v>
+        <v>107500</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>128305408</v>
       </c>
       <c r="B31" t="n">
-        <v>106902</v>
+        <v>106911</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3995,10 +3995,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128305378</v>
+        <v>128305410</v>
       </c>
       <c r="B32" t="n">
-        <v>106902</v>
+        <v>104069</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4006,21 +4006,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4030,10 +4030,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>704248</v>
+        <v>704471</v>
       </c>
       <c r="R32" t="n">
-        <v>6359861</v>
+        <v>6359883</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4097,10 +4097,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128305410</v>
+        <v>128305378</v>
       </c>
       <c r="B33" t="n">
-        <v>104060</v>
+        <v>106911</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,21 +4108,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>704471</v>
+        <v>704248</v>
       </c>
       <c r="R33" t="n">
-        <v>6359883</v>
+        <v>6359861</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4202,7 +4202,7 @@
         <v>128305384</v>
       </c>
       <c r="B34" t="n">
-        <v>98616</v>
+        <v>98619</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>128305411</v>
       </c>
       <c r="B35" t="n">
-        <v>106902</v>
+        <v>106911</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>128305475</v>
       </c>
       <c r="B36" t="n">
-        <v>106902</v>
+        <v>106911</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>128305413</v>
       </c>
       <c r="B37" t="n">
-        <v>104060</v>
+        <v>104069</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>128305423</v>
       </c>
       <c r="B38" t="n">
-        <v>106902</v>
+        <v>106911</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>128305407</v>
       </c>
       <c r="B39" t="n">
-        <v>104060</v>
+        <v>104069</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4820,10 +4820,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128305381</v>
+        <v>128305483</v>
       </c>
       <c r="B40" t="n">
-        <v>107491</v>
+        <v>106911</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4831,31 +4831,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>704287</v>
+        <v>704298</v>
       </c>
       <c r="R40" t="n">
-        <v>6359876</v>
+        <v>6360088</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4931,10 +4931,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128305483</v>
+        <v>128305381</v>
       </c>
       <c r="B41" t="n">
-        <v>106902</v>
+        <v>107500</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4942,31 +4942,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4975,10 +4975,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>704298</v>
+        <v>704287</v>
       </c>
       <c r="R41" t="n">
-        <v>6360088</v>
+        <v>6359876</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5045,7 +5045,7 @@
         <v>128305490</v>
       </c>
       <c r="B42" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>128305414</v>
       </c>
       <c r="B43" t="n">
-        <v>106902</v>
+        <v>106911</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 569-2023 artfynd.xlsx
+++ b/artfynd/A 569-2023 artfynd.xlsx
@@ -5042,10 +5042,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128305490</v>
+        <v>128305414</v>
       </c>
       <c r="B42" t="n">
-        <v>109444</v>
+        <v>106911</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5053,16 +5053,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>704264</v>
+        <v>704517</v>
       </c>
       <c r="R42" t="n">
-        <v>6360097</v>
+        <v>6359895</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5144,10 +5144,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128305414</v>
+        <v>128305490</v>
       </c>
       <c r="B43" t="n">
-        <v>106911</v>
+        <v>109444</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5155,16 +5155,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>704517</v>
+        <v>704264</v>
       </c>
       <c r="R43" t="n">
-        <v>6359895</v>
+        <v>6360097</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 569-2023 artfynd.xlsx
+++ b/artfynd/A 569-2023 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>128305487</v>
       </c>
       <c r="B23" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>128305385</v>
       </c>
       <c r="B24" t="n">
-        <v>106911</v>
+        <v>106916</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>128305390</v>
       </c>
       <c r="B25" t="n">
-        <v>106911</v>
+        <v>106916</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128305426</v>
+        <v>128305377</v>
       </c>
       <c r="B26" t="n">
-        <v>107500</v>
+        <v>109449</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3367,26 +3367,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>704548</v>
+        <v>704248</v>
       </c>
       <c r="R26" t="n">
-        <v>6359959</v>
+        <v>6359861</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128305478</v>
+        <v>128305426</v>
       </c>
       <c r="B27" t="n">
-        <v>106911</v>
+        <v>107505</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3478,34 +3478,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>704346</v>
+        <v>704548</v>
       </c>
       <c r="R27" t="n">
-        <v>6360116</v>
+        <v>6359959</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3569,10 +3578,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128305377</v>
+        <v>128305478</v>
       </c>
       <c r="B28" t="n">
-        <v>109444</v>
+        <v>106916</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3580,16 +3589,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3597,26 +3606,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>704248</v>
+        <v>704346</v>
       </c>
       <c r="R28" t="n">
-        <v>6359861</v>
+        <v>6360116</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3683,7 +3683,7 @@
         <v>128305421</v>
       </c>
       <c r="B29" t="n">
-        <v>104069</v>
+        <v>104072</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>128305424</v>
       </c>
       <c r="B30" t="n">
-        <v>107500</v>
+        <v>107505</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>128305408</v>
       </c>
       <c r="B31" t="n">
-        <v>106911</v>
+        <v>106916</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3995,10 +3995,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128305410</v>
+        <v>128305378</v>
       </c>
       <c r="B32" t="n">
-        <v>104069</v>
+        <v>106916</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4006,21 +4006,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4030,10 +4030,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>704471</v>
+        <v>704248</v>
       </c>
       <c r="R32" t="n">
-        <v>6359883</v>
+        <v>6359861</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4097,10 +4097,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128305378</v>
+        <v>128305410</v>
       </c>
       <c r="B33" t="n">
-        <v>106911</v>
+        <v>104072</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,21 +4108,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>704248</v>
+        <v>704471</v>
       </c>
       <c r="R33" t="n">
-        <v>6359861</v>
+        <v>6359883</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4202,7 +4202,7 @@
         <v>128305384</v>
       </c>
       <c r="B34" t="n">
-        <v>98619</v>
+        <v>98620</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>128305411</v>
       </c>
       <c r="B35" t="n">
-        <v>106911</v>
+        <v>106916</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>128305475</v>
       </c>
       <c r="B36" t="n">
-        <v>106911</v>
+        <v>106916</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>128305413</v>
       </c>
       <c r="B37" t="n">
-        <v>104069</v>
+        <v>104072</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>128305423</v>
       </c>
       <c r="B38" t="n">
-        <v>106911</v>
+        <v>106916</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>128305407</v>
       </c>
       <c r="B39" t="n">
-        <v>104069</v>
+        <v>104072</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4820,10 +4820,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128305483</v>
+        <v>128305381</v>
       </c>
       <c r="B40" t="n">
-        <v>106911</v>
+        <v>107505</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4831,31 +4831,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>704298</v>
+        <v>704287</v>
       </c>
       <c r="R40" t="n">
-        <v>6360088</v>
+        <v>6359876</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4931,10 +4931,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128305381</v>
+        <v>128305483</v>
       </c>
       <c r="B41" t="n">
-        <v>107500</v>
+        <v>106916</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4942,31 +4942,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4975,10 +4975,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>704287</v>
+        <v>704298</v>
       </c>
       <c r="R41" t="n">
-        <v>6359876</v>
+        <v>6360088</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5042,10 +5042,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128305414</v>
+        <v>128305490</v>
       </c>
       <c r="B42" t="n">
-        <v>106911</v>
+        <v>109449</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5053,16 +5053,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>704517</v>
+        <v>704264</v>
       </c>
       <c r="R42" t="n">
-        <v>6359895</v>
+        <v>6360097</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5144,10 +5144,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128305490</v>
+        <v>128305414</v>
       </c>
       <c r="B43" t="n">
-        <v>109444</v>
+        <v>106916</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5155,16 +5155,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>704264</v>
+        <v>704517</v>
       </c>
       <c r="R43" t="n">
-        <v>6360097</v>
+        <v>6359895</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 569-2023 artfynd.xlsx
+++ b/artfynd/A 569-2023 artfynd.xlsx
@@ -3356,10 +3356,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128305377</v>
+        <v>128305426</v>
       </c>
       <c r="B26" t="n">
-        <v>109449</v>
+        <v>107505</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3367,26 +3367,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>704248</v>
+        <v>704548</v>
       </c>
       <c r="R26" t="n">
-        <v>6359861</v>
+        <v>6359959</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128305426</v>
+        <v>128305377</v>
       </c>
       <c r="B27" t="n">
-        <v>107505</v>
+        <v>109449</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3478,26 +3478,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>704548</v>
+        <v>704248</v>
       </c>
       <c r="R27" t="n">
-        <v>6359959</v>
+        <v>6359861</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3995,10 +3995,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128305378</v>
+        <v>128305410</v>
       </c>
       <c r="B32" t="n">
-        <v>106916</v>
+        <v>104072</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4006,21 +4006,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4030,10 +4030,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>704248</v>
+        <v>704471</v>
       </c>
       <c r="R32" t="n">
-        <v>6359861</v>
+        <v>6359883</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4097,10 +4097,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128305410</v>
+        <v>128305378</v>
       </c>
       <c r="B33" t="n">
-        <v>104072</v>
+        <v>106916</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,21 +4108,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>704471</v>
+        <v>704248</v>
       </c>
       <c r="R33" t="n">
-        <v>6359883</v>
+        <v>6359861</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4820,10 +4820,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128305381</v>
+        <v>128305483</v>
       </c>
       <c r="B40" t="n">
-        <v>107505</v>
+        <v>106916</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4831,31 +4831,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>704287</v>
+        <v>704298</v>
       </c>
       <c r="R40" t="n">
-        <v>6359876</v>
+        <v>6360088</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4931,10 +4931,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128305483</v>
+        <v>128305381</v>
       </c>
       <c r="B41" t="n">
-        <v>106916</v>
+        <v>107505</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4942,31 +4942,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4975,10 +4975,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>704298</v>
+        <v>704287</v>
       </c>
       <c r="R41" t="n">
-        <v>6360088</v>
+        <v>6359876</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>

--- a/artfynd/A 569-2023 artfynd.xlsx
+++ b/artfynd/A 569-2023 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>128305487</v>
       </c>
       <c r="B23" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>128305385</v>
       </c>
       <c r="B24" t="n">
-        <v>106916</v>
+        <v>106944</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>128305390</v>
       </c>
       <c r="B25" t="n">
-        <v>106916</v>
+        <v>106944</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128305426</v>
+        <v>128305377</v>
       </c>
       <c r="B26" t="n">
-        <v>107505</v>
+        <v>109477</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3367,26 +3367,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>704548</v>
+        <v>704248</v>
       </c>
       <c r="R26" t="n">
-        <v>6359959</v>
+        <v>6359861</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128305377</v>
+        <v>128305426</v>
       </c>
       <c r="B27" t="n">
-        <v>109449</v>
+        <v>107533</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3478,26 +3478,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>704248</v>
+        <v>704548</v>
       </c>
       <c r="R27" t="n">
-        <v>6359861</v>
+        <v>6359959</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3581,7 +3581,7 @@
         <v>128305478</v>
       </c>
       <c r="B28" t="n">
-        <v>106916</v>
+        <v>106944</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>128305421</v>
       </c>
       <c r="B29" t="n">
-        <v>104072</v>
+        <v>104099</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>128305424</v>
       </c>
       <c r="B30" t="n">
-        <v>107505</v>
+        <v>107533</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>128305408</v>
       </c>
       <c r="B31" t="n">
-        <v>106916</v>
+        <v>106944</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3995,10 +3995,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128305410</v>
+        <v>128305378</v>
       </c>
       <c r="B32" t="n">
-        <v>104072</v>
+        <v>106944</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4006,21 +4006,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4030,10 +4030,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>704471</v>
+        <v>704248</v>
       </c>
       <c r="R32" t="n">
-        <v>6359883</v>
+        <v>6359861</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4097,10 +4097,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128305378</v>
+        <v>128305410</v>
       </c>
       <c r="B33" t="n">
-        <v>106916</v>
+        <v>104099</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,21 +4108,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>704248</v>
+        <v>704471</v>
       </c>
       <c r="R33" t="n">
-        <v>6359861</v>
+        <v>6359883</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4202,7 +4202,7 @@
         <v>128305384</v>
       </c>
       <c r="B34" t="n">
-        <v>98620</v>
+        <v>98647</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>128305411</v>
       </c>
       <c r="B35" t="n">
-        <v>106916</v>
+        <v>106944</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>128305475</v>
       </c>
       <c r="B36" t="n">
-        <v>106916</v>
+        <v>106944</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>128305413</v>
       </c>
       <c r="B37" t="n">
-        <v>104072</v>
+        <v>104099</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>128305423</v>
       </c>
       <c r="B38" t="n">
-        <v>106916</v>
+        <v>106944</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>128305407</v>
       </c>
       <c r="B39" t="n">
-        <v>104072</v>
+        <v>104099</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4820,10 +4820,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128305483</v>
+        <v>128305381</v>
       </c>
       <c r="B40" t="n">
-        <v>106916</v>
+        <v>107533</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4831,31 +4831,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>704298</v>
+        <v>704287</v>
       </c>
       <c r="R40" t="n">
-        <v>6360088</v>
+        <v>6359876</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4931,10 +4931,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128305381</v>
+        <v>128305483</v>
       </c>
       <c r="B41" t="n">
-        <v>107505</v>
+        <v>106944</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4942,31 +4942,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4975,10 +4975,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>704287</v>
+        <v>704298</v>
       </c>
       <c r="R41" t="n">
-        <v>6359876</v>
+        <v>6360088</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5045,7 +5045,7 @@
         <v>128305490</v>
       </c>
       <c r="B42" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>128305414</v>
       </c>
       <c r="B43" t="n">
-        <v>106916</v>
+        <v>106944</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 569-2023 artfynd.xlsx
+++ b/artfynd/A 569-2023 artfynd.xlsx
@@ -3356,10 +3356,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128305377</v>
+        <v>128305426</v>
       </c>
       <c r="B26" t="n">
-        <v>109477</v>
+        <v>107533</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3367,26 +3367,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>704248</v>
+        <v>704548</v>
       </c>
       <c r="R26" t="n">
-        <v>6359861</v>
+        <v>6359959</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128305426</v>
+        <v>128305478</v>
       </c>
       <c r="B27" t="n">
-        <v>107533</v>
+        <v>106944</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3478,43 +3478,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>704548</v>
+        <v>704346</v>
       </c>
       <c r="R27" t="n">
-        <v>6359959</v>
+        <v>6360116</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3578,10 +3569,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128305478</v>
+        <v>128305377</v>
       </c>
       <c r="B28" t="n">
-        <v>106944</v>
+        <v>109477</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3589,16 +3580,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3606,17 +3597,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>704346</v>
+        <v>704248</v>
       </c>
       <c r="R28" t="n">
-        <v>6360116</v>
+        <v>6359861</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3995,10 +3995,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128305378</v>
+        <v>128305410</v>
       </c>
       <c r="B32" t="n">
-        <v>106944</v>
+        <v>104099</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4006,21 +4006,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4030,10 +4030,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>704248</v>
+        <v>704471</v>
       </c>
       <c r="R32" t="n">
-        <v>6359861</v>
+        <v>6359883</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4097,10 +4097,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128305410</v>
+        <v>128305378</v>
       </c>
       <c r="B33" t="n">
-        <v>104099</v>
+        <v>106944</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,21 +4108,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>704471</v>
+        <v>704248</v>
       </c>
       <c r="R33" t="n">
-        <v>6359883</v>
+        <v>6359861</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128305413</v>
+        <v>128305423</v>
       </c>
       <c r="B37" t="n">
-        <v>104099</v>
+        <v>106944</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4525,21 +4525,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4549,10 +4549,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>704517</v>
+        <v>704541</v>
       </c>
       <c r="R37" t="n">
-        <v>6359895</v>
+        <v>6359927</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128305423</v>
+        <v>128305413</v>
       </c>
       <c r="B38" t="n">
-        <v>106944</v>
+        <v>104099</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4627,21 +4627,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4651,10 +4651,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>704541</v>
+        <v>704517</v>
       </c>
       <c r="R38" t="n">
-        <v>6359927</v>
+        <v>6359895</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>

--- a/artfynd/A 569-2023 artfynd.xlsx
+++ b/artfynd/A 569-2023 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>128305487</v>
       </c>
       <c r="B23" t="n">
-        <v>109477</v>
+        <v>109490</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,10 +3152,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128305385</v>
+        <v>128305390</v>
       </c>
       <c r="B24" t="n">
-        <v>106944</v>
+        <v>106957</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>704296</v>
+        <v>704316</v>
       </c>
       <c r="R24" t="n">
-        <v>6359878</v>
+        <v>6359869</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3254,10 +3254,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128305390</v>
+        <v>128305385</v>
       </c>
       <c r="B25" t="n">
-        <v>106944</v>
+        <v>106957</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>704316</v>
+        <v>704296</v>
       </c>
       <c r="R25" t="n">
-        <v>6359869</v>
+        <v>6359878</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128305426</v>
+        <v>128305377</v>
       </c>
       <c r="B26" t="n">
-        <v>107533</v>
+        <v>109490</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3367,26 +3367,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>704548</v>
+        <v>704248</v>
       </c>
       <c r="R26" t="n">
-        <v>6359959</v>
+        <v>6359861</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128305478</v>
+        <v>128305426</v>
       </c>
       <c r="B27" t="n">
-        <v>106944</v>
+        <v>107546</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3478,34 +3478,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>704346</v>
+        <v>704548</v>
       </c>
       <c r="R27" t="n">
-        <v>6360116</v>
+        <v>6359959</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3569,10 +3578,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128305377</v>
+        <v>128305478</v>
       </c>
       <c r="B28" t="n">
-        <v>109477</v>
+        <v>106957</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3580,16 +3589,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3597,26 +3606,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>704248</v>
+        <v>704346</v>
       </c>
       <c r="R28" t="n">
-        <v>6359861</v>
+        <v>6360116</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3683,7 +3683,7 @@
         <v>128305421</v>
       </c>
       <c r="B29" t="n">
-        <v>104099</v>
+        <v>104112</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>128305424</v>
       </c>
       <c r="B30" t="n">
-        <v>107533</v>
+        <v>107546</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>128305408</v>
       </c>
       <c r="B31" t="n">
-        <v>106944</v>
+        <v>106957</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3995,10 +3995,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128305410</v>
+        <v>128305378</v>
       </c>
       <c r="B32" t="n">
-        <v>104099</v>
+        <v>106957</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4006,21 +4006,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4030,10 +4030,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>704471</v>
+        <v>704248</v>
       </c>
       <c r="R32" t="n">
-        <v>6359883</v>
+        <v>6359861</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4097,10 +4097,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128305378</v>
+        <v>128305410</v>
       </c>
       <c r="B33" t="n">
-        <v>106944</v>
+        <v>104112</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,21 +4108,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>704248</v>
+        <v>704471</v>
       </c>
       <c r="R33" t="n">
-        <v>6359861</v>
+        <v>6359883</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4202,7 +4202,7 @@
         <v>128305384</v>
       </c>
       <c r="B34" t="n">
-        <v>98647</v>
+        <v>98660</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>128305411</v>
       </c>
       <c r="B35" t="n">
-        <v>106944</v>
+        <v>106957</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>128305475</v>
       </c>
       <c r="B36" t="n">
-        <v>106944</v>
+        <v>106957</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4514,10 +4514,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128305423</v>
+        <v>128305413</v>
       </c>
       <c r="B37" t="n">
-        <v>106944</v>
+        <v>104112</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4525,21 +4525,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4549,10 +4549,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>704541</v>
+        <v>704517</v>
       </c>
       <c r="R37" t="n">
-        <v>6359927</v>
+        <v>6359895</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128305413</v>
+        <v>128305423</v>
       </c>
       <c r="B38" t="n">
-        <v>104099</v>
+        <v>106957</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4627,21 +4627,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4651,10 +4651,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>704517</v>
+        <v>704541</v>
       </c>
       <c r="R38" t="n">
-        <v>6359895</v>
+        <v>6359927</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4721,7 +4721,7 @@
         <v>128305407</v>
       </c>
       <c r="B39" t="n">
-        <v>104099</v>
+        <v>104112</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>128305381</v>
       </c>
       <c r="B40" t="n">
-        <v>107533</v>
+        <v>107546</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>128305483</v>
       </c>
       <c r="B41" t="n">
-        <v>106944</v>
+        <v>106957</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5042,10 +5042,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128305490</v>
+        <v>128305414</v>
       </c>
       <c r="B42" t="n">
-        <v>109477</v>
+        <v>106957</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5053,16 +5053,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>704264</v>
+        <v>704517</v>
       </c>
       <c r="R42" t="n">
-        <v>6360097</v>
+        <v>6359895</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5144,10 +5144,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128305414</v>
+        <v>128305490</v>
       </c>
       <c r="B43" t="n">
-        <v>106944</v>
+        <v>109490</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5155,16 +5155,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>704517</v>
+        <v>704264</v>
       </c>
       <c r="R43" t="n">
-        <v>6359895</v>
+        <v>6360097</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 569-2023 artfynd.xlsx
+++ b/artfynd/A 569-2023 artfynd.xlsx
@@ -3152,7 +3152,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128305390</v>
+        <v>128305385</v>
       </c>
       <c r="B24" t="n">
         <v>106957</v>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>704316</v>
+        <v>704296</v>
       </c>
       <c r="R24" t="n">
-        <v>6359869</v>
+        <v>6359878</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3254,7 +3254,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128305385</v>
+        <v>128305390</v>
       </c>
       <c r="B25" t="n">
         <v>106957</v>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>704296</v>
+        <v>704316</v>
       </c>
       <c r="R25" t="n">
-        <v>6359878</v>
+        <v>6359869</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128305377</v>
+        <v>128305478</v>
       </c>
       <c r="B26" t="n">
-        <v>109490</v>
+        <v>106957</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3367,16 +3367,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3384,26 +3384,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>704248</v>
+        <v>704346</v>
       </c>
       <c r="R26" t="n">
-        <v>6359861</v>
+        <v>6360116</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3467,10 +3458,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128305426</v>
+        <v>128305377</v>
       </c>
       <c r="B27" t="n">
-        <v>107546</v>
+        <v>109490</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3478,26 +3469,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3511,10 +3502,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>704548</v>
+        <v>704248</v>
       </c>
       <c r="R27" t="n">
-        <v>6359959</v>
+        <v>6359861</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3578,10 +3569,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128305478</v>
+        <v>128305426</v>
       </c>
       <c r="B28" t="n">
-        <v>106957</v>
+        <v>107546</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3589,34 +3580,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>704346</v>
+        <v>704548</v>
       </c>
       <c r="R28" t="n">
-        <v>6360116</v>
+        <v>6359959</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3995,10 +3995,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128305378</v>
+        <v>128305410</v>
       </c>
       <c r="B32" t="n">
-        <v>106957</v>
+        <v>104112</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4006,21 +4006,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4030,10 +4030,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>704248</v>
+        <v>704471</v>
       </c>
       <c r="R32" t="n">
-        <v>6359861</v>
+        <v>6359883</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4097,10 +4097,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128305410</v>
+        <v>128305378</v>
       </c>
       <c r="B33" t="n">
-        <v>104112</v>
+        <v>106957</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,21 +4108,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>704471</v>
+        <v>704248</v>
       </c>
       <c r="R33" t="n">
-        <v>6359883</v>
+        <v>6359861</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5042,10 +5042,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128305414</v>
+        <v>128305490</v>
       </c>
       <c r="B42" t="n">
-        <v>106957</v>
+        <v>109490</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5053,16 +5053,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>704517</v>
+        <v>704264</v>
       </c>
       <c r="R42" t="n">
-        <v>6359895</v>
+        <v>6360097</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5144,10 +5144,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128305490</v>
+        <v>128305414</v>
       </c>
       <c r="B43" t="n">
-        <v>109490</v>
+        <v>106957</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5155,16 +5155,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>704264</v>
+        <v>704517</v>
       </c>
       <c r="R43" t="n">
-        <v>6360097</v>
+        <v>6359895</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 569-2023 artfynd.xlsx
+++ b/artfynd/A 569-2023 artfynd.xlsx
@@ -4820,10 +4820,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128305381</v>
+        <v>128305483</v>
       </c>
       <c r="B40" t="n">
-        <v>107546</v>
+        <v>106957</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4831,31 +4831,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>704287</v>
+        <v>704298</v>
       </c>
       <c r="R40" t="n">
-        <v>6359876</v>
+        <v>6360088</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4931,10 +4931,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128305483</v>
+        <v>128305381</v>
       </c>
       <c r="B41" t="n">
-        <v>106957</v>
+        <v>107546</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4942,31 +4942,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4975,10 +4975,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>704298</v>
+        <v>704287</v>
       </c>
       <c r="R41" t="n">
-        <v>6360088</v>
+        <v>6359876</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5042,10 +5042,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128305490</v>
+        <v>128305414</v>
       </c>
       <c r="B42" t="n">
-        <v>109490</v>
+        <v>106957</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5053,16 +5053,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>704264</v>
+        <v>704517</v>
       </c>
       <c r="R42" t="n">
-        <v>6360097</v>
+        <v>6359895</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5144,10 +5144,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128305414</v>
+        <v>128305490</v>
       </c>
       <c r="B43" t="n">
-        <v>106957</v>
+        <v>109490</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5155,16 +5155,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>704517</v>
+        <v>704264</v>
       </c>
       <c r="R43" t="n">
-        <v>6359895</v>
+        <v>6360097</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 569-2023 artfynd.xlsx
+++ b/artfynd/A 569-2023 artfynd.xlsx
@@ -3356,10 +3356,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128305478</v>
+        <v>128305377</v>
       </c>
       <c r="B26" t="n">
-        <v>106957</v>
+        <v>109490</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3367,16 +3367,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3384,17 +3384,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>704346</v>
+        <v>704248</v>
       </c>
       <c r="R26" t="n">
-        <v>6360116</v>
+        <v>6359861</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3458,10 +3467,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128305377</v>
+        <v>128305426</v>
       </c>
       <c r="B27" t="n">
-        <v>109490</v>
+        <v>107546</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3469,26 +3478,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3502,10 +3511,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>704248</v>
+        <v>704548</v>
       </c>
       <c r="R27" t="n">
-        <v>6359861</v>
+        <v>6359959</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3569,10 +3578,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128305426</v>
+        <v>128305478</v>
       </c>
       <c r="B28" t="n">
-        <v>107546</v>
+        <v>106957</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3580,43 +3589,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>704548</v>
+        <v>704346</v>
       </c>
       <c r="R28" t="n">
-        <v>6359959</v>
+        <v>6360116</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4820,10 +4820,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128305483</v>
+        <v>128305381</v>
       </c>
       <c r="B40" t="n">
-        <v>106957</v>
+        <v>107546</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4831,31 +4831,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>704298</v>
+        <v>704287</v>
       </c>
       <c r="R40" t="n">
-        <v>6360088</v>
+        <v>6359876</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4931,10 +4931,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128305381</v>
+        <v>128305483</v>
       </c>
       <c r="B41" t="n">
-        <v>107546</v>
+        <v>106957</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4942,31 +4942,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4975,10 +4975,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>704287</v>
+        <v>704298</v>
       </c>
       <c r="R41" t="n">
-        <v>6359876</v>
+        <v>6360088</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5042,10 +5042,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128305414</v>
+        <v>128305490</v>
       </c>
       <c r="B42" t="n">
-        <v>106957</v>
+        <v>109490</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5053,16 +5053,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>704517</v>
+        <v>704264</v>
       </c>
       <c r="R42" t="n">
-        <v>6359895</v>
+        <v>6360097</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5144,10 +5144,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128305490</v>
+        <v>128305414</v>
       </c>
       <c r="B43" t="n">
-        <v>109490</v>
+        <v>106957</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5155,16 +5155,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>704264</v>
+        <v>704517</v>
       </c>
       <c r="R43" t="n">
-        <v>6360097</v>
+        <v>6359895</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 569-2023 artfynd.xlsx
+++ b/artfynd/A 569-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13185311</v>
+        <v>96223990</v>
       </c>
       <c r="B2" t="n">
-        <v>42759</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101242</v>
+        <v>433</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>lojsta, Gtl</t>
+          <t>Lojsta Klint söder, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>704362.7641989777</v>
+        <v>704108</v>
       </c>
       <c r="R2" t="n">
-        <v>6359775.976300949</v>
+        <v>6359932</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,22 +736,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2006-07-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2006-07-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,12 +756,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -799,12 +771,7 @@
         <v>96223991</v>
       </c>
       <c r="B3" t="n">
-        <v>85172</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +803,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>704297.2402363643</v>
+        <v>704297</v>
       </c>
       <c r="R3" t="n">
-        <v>6360100.886396431</v>
+        <v>6360101</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,19 +836,9 @@
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,37 +865,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96223999</v>
+        <v>96223985</v>
       </c>
       <c r="B4" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +900,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>704142.5456162975</v>
+        <v>704271</v>
       </c>
       <c r="R4" t="n">
-        <v>6359868.251841524</v>
+        <v>6359990</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,19 +933,9 @@
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,37 +962,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96223975</v>
+        <v>96223957</v>
       </c>
       <c r="B5" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90801</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>248956</v>
+        <v>655</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Schaeff.) With., nom sanct.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +997,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>704309.4965992414</v>
+        <v>704360</v>
       </c>
       <c r="R5" t="n">
-        <v>6360039.864874749</v>
+        <v>6360057</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,19 +1030,9 @@
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,37 +1059,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96223974</v>
+        <v>96223966</v>
       </c>
       <c r="B6" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230185</v>
+        <v>1985</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1094,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>704356.427377074</v>
+        <v>704284</v>
       </c>
       <c r="R6" t="n">
-        <v>6360043.830811254</v>
+        <v>6360104</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,19 +1127,9 @@
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,15 +1156,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96223993</v>
+        <v>96223953</v>
       </c>
       <c r="B7" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,21 +1167,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3712</v>
+        <v>3215</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,10 +1191,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>704091.433459552</v>
+        <v>704298</v>
       </c>
       <c r="R7" t="n">
-        <v>6359904.629843276</v>
+        <v>6359912</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,19 +1224,9 @@
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,37 +1253,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96223985</v>
+        <v>96223954</v>
       </c>
       <c r="B8" t="n">
-        <v>85194</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>449</v>
+        <v>3215</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,10 +1288,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>704271.3659007481</v>
+        <v>704421</v>
       </c>
       <c r="R8" t="n">
-        <v>6359989.842746416</v>
+        <v>6360001</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,19 +1321,9 @@
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,37 +1350,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96223954</v>
+        <v>96223986</v>
       </c>
       <c r="B9" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3215</v>
+        <v>3286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1385,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>704421.373032182</v>
+        <v>704297</v>
       </c>
       <c r="R9" t="n">
-        <v>6360001.660567175</v>
+        <v>6360012</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,19 +1418,9 @@
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,15 +1447,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96223953</v>
+        <v>96223999</v>
       </c>
       <c r="B10" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,21 +1458,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1482,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>704297.9933228352</v>
+        <v>704143</v>
       </c>
       <c r="R10" t="n">
-        <v>6359912.235831269</v>
+        <v>6359868</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,19 +1515,9 @@
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,37 +1544,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96223990</v>
+        <v>96224000</v>
       </c>
       <c r="B11" t="n">
-        <v>85148</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>433</v>
+        <v>3674</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1732,10 +1579,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>704107.9476229344</v>
+        <v>704267</v>
       </c>
       <c r="R11" t="n">
-        <v>6359931.946125066</v>
+        <v>6360007</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1765,19 +1612,9 @@
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,15 +1641,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96223995</v>
+        <v>96224001</v>
       </c>
       <c r="B12" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,21 +1652,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>704310.9898191143</v>
+        <v>704297</v>
       </c>
       <c r="R12" t="n">
-        <v>6360085.894409774</v>
+        <v>6360102</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,19 +1709,9 @@
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,37 +1738,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96224001</v>
+        <v>96223993</v>
       </c>
       <c r="B13" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1956,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>704297.1863736704</v>
+        <v>704091</v>
       </c>
       <c r="R13" t="n">
-        <v>6360101.964989394</v>
+        <v>6359904</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1989,19 +1806,9 @@
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,15 +1835,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96223951</v>
+        <v>96223994</v>
       </c>
       <c r="B14" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,21 +1846,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>3712</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2068,10 +1870,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>704346.2714493219</v>
+        <v>704281</v>
       </c>
       <c r="R14" t="n">
-        <v>6360062.786866338</v>
+        <v>6360105</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2101,19 +1903,9 @@
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,37 +1932,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96223996</v>
+        <v>96223995</v>
       </c>
       <c r="B15" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6031</v>
+        <v>3712</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2180,10 +1967,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>704147.2960910397</v>
+        <v>704311</v>
       </c>
       <c r="R15" t="n">
-        <v>6359979.32462847</v>
+        <v>6360086</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2213,19 +2000,9 @@
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,15 +2029,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>96223986</v>
+        <v>96290689</v>
       </c>
       <c r="B16" t="n">
-        <v>88886</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2268,34 +2040,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3286</v>
+        <v>3712</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lojsta Klint söder, Gtl</t>
+          <t>Lojsta klints, stångkvie, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>704296.7937038318</v>
+        <v>704465</v>
       </c>
       <c r="R16" t="n">
-        <v>6360012.197950171</v>
+        <v>6360053</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2322,22 +2094,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,37 +2126,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96223966</v>
+        <v>96223996</v>
       </c>
       <c r="B17" t="n">
-        <v>85057</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1985</v>
+        <v>6031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2404,10 +2161,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>704284.0832046376</v>
+        <v>704148</v>
       </c>
       <c r="R17" t="n">
-        <v>6360104.013870368</v>
+        <v>6359979</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2437,19 +2194,9 @@
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,50 +2223,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96224000</v>
+        <v>13185311</v>
       </c>
       <c r="B18" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3674</v>
+        <v>101242</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lojsta Klint söder, Gtl</t>
+          <t>lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>704267.2889397769</v>
+        <v>704363</v>
       </c>
       <c r="R18" t="n">
-        <v>6360006.399474182</v>
+        <v>6359776</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2546,22 +2297,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-07-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-07-04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2576,27 +2317,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>96223994</v>
+        <v>128305384</v>
       </c>
       <c r="B19" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,37 +2340,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3712</v>
+        <v>219864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lojsta Klint söder, Gtl</t>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>704280.7872179797</v>
+        <v>704296</v>
       </c>
       <c r="R19" t="n">
-        <v>6360104.930568847</v>
+        <v>6359878</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2658,22 +2403,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2684,69 +2419,78 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>96223957</v>
+        <v>128305428</v>
       </c>
       <c r="B20" t="n">
-        <v>88270</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>655</v>
+        <v>219864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fistulina hepatica</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) With., nom sanct.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lojsta Klint söder, Gtl</t>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>704360.6710314947</v>
+        <v>704514</v>
       </c>
       <c r="R20" t="n">
-        <v>6360056.477718582</v>
+        <v>6360038</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2770,22 +2514,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2796,53 +2530,53 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96223977</v>
+        <v>96223970</v>
       </c>
       <c r="B21" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>248956</v>
+        <v>220079</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2852,10 +2586,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>704296.0518012417</v>
+        <v>704426</v>
       </c>
       <c r="R21" t="n">
-        <v>6360102.989613803</v>
+        <v>6359885</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2885,19 +2619,9 @@
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,53 +2648,57 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>96290689</v>
+        <v>128305381</v>
       </c>
       <c r="B22" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3712</v>
+        <v>220079</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lojsta klints, stångkvie, Gtl</t>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>704464.3112329226</v>
+        <v>704287</v>
       </c>
       <c r="R22" t="n">
-        <v>6360053.005741274</v>
+        <v>6359876</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2994,22 +2722,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3020,26 +2738,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128305487</v>
+        <v>128305392</v>
       </c>
       <c r="B23" t="n">
-        <v>109490</v>
+        <v>108116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3047,21 +2770,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3080,10 +2803,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>704285</v>
+        <v>704369</v>
       </c>
       <c r="R23" t="n">
-        <v>6360090</v>
+        <v>6359867</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3116,11 +2839,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Pansartall, levande, med flagnande bark och en del insektshål.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,10 +2870,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128305385</v>
+        <v>128305403</v>
       </c>
       <c r="B24" t="n">
-        <v>106957</v>
+        <v>108116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3163,37 +2881,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>704296</v>
+        <v>704436</v>
       </c>
       <c r="R24" t="n">
-        <v>6359878</v>
+        <v>6359870</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3254,10 +2981,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128305390</v>
+        <v>128305424</v>
       </c>
       <c r="B25" t="n">
-        <v>106957</v>
+        <v>108116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3265,34 +2992,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>704316</v>
+        <v>704541</v>
       </c>
       <c r="R25" t="n">
-        <v>6359869</v>
+        <v>6359927</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3356,10 +3092,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128305377</v>
+        <v>128305426</v>
       </c>
       <c r="B26" t="n">
-        <v>109490</v>
+        <v>108116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3367,26 +3103,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3400,10 +3136,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>704248</v>
+        <v>704548</v>
       </c>
       <c r="R26" t="n">
-        <v>6359861</v>
+        <v>6359959</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3467,10 +3203,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128305426</v>
+        <v>128305467</v>
       </c>
       <c r="B27" t="n">
-        <v>107546</v>
+        <v>108116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3497,7 +3233,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3511,10 +3247,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>704548</v>
+        <v>704449</v>
       </c>
       <c r="R27" t="n">
-        <v>6359959</v>
+        <v>6360193</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3578,10 +3314,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128305478</v>
+        <v>128305469</v>
       </c>
       <c r="B28" t="n">
-        <v>106957</v>
+        <v>108116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3589,34 +3325,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>704346</v>
+        <v>704446</v>
       </c>
       <c r="R28" t="n">
-        <v>6360116</v>
+        <v>6360188</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3680,10 +3425,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128305421</v>
+        <v>128305394</v>
       </c>
       <c r="B29" t="n">
-        <v>104112</v>
+        <v>104640</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3715,10 +3460,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>704541</v>
+        <v>704369</v>
       </c>
       <c r="R29" t="n">
-        <v>6359927</v>
+        <v>6359867</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3782,10 +3527,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128305424</v>
+        <v>128305404</v>
       </c>
       <c r="B30" t="n">
-        <v>107546</v>
+        <v>104640</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3793,43 +3538,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220079</v>
+        <v>220164</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>704541</v>
+        <v>704436</v>
       </c>
       <c r="R30" t="n">
-        <v>6359927</v>
+        <v>6359870</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3893,10 +3629,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128305408</v>
+        <v>128305407</v>
       </c>
       <c r="B31" t="n">
-        <v>106957</v>
+        <v>104640</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3904,21 +3640,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3998,7 +3734,7 @@
         <v>128305410</v>
       </c>
       <c r="B32" t="n">
-        <v>104112</v>
+        <v>104640</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4097,10 +3833,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128305378</v>
+        <v>128305413</v>
       </c>
       <c r="B33" t="n">
-        <v>106957</v>
+        <v>104640</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,21 +3844,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4132,10 +3868,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>704248</v>
+        <v>704517</v>
       </c>
       <c r="R33" t="n">
-        <v>6359861</v>
+        <v>6359895</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4181,7 +3917,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4199,54 +3935,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128305384</v>
+        <v>128305417</v>
       </c>
       <c r="B34" t="n">
-        <v>98660</v>
+        <v>104640</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219864</v>
+        <v>220164</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>704296</v>
+        <v>704529</v>
       </c>
       <c r="R34" t="n">
-        <v>6359878</v>
+        <v>6359868</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4292,7 +4019,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4310,10 +4037,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128305411</v>
+        <v>128305421</v>
       </c>
       <c r="B35" t="n">
-        <v>106957</v>
+        <v>104640</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4321,21 +4048,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4345,10 +4072,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>704471</v>
+        <v>704541</v>
       </c>
       <c r="R35" t="n">
-        <v>6359883</v>
+        <v>6359927</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4394,7 +4121,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4412,10 +4139,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128305475</v>
+        <v>128305468</v>
       </c>
       <c r="B36" t="n">
-        <v>106957</v>
+        <v>104640</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4423,21 +4150,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4447,13 +4174,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>704379</v>
+        <v>704446</v>
       </c>
       <c r="R36" t="n">
-        <v>6360148</v>
+        <v>6360188</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4514,10 +4241,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128305413</v>
+        <v>128305372</v>
       </c>
       <c r="B37" t="n">
-        <v>104112</v>
+        <v>110078</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4525,34 +4252,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220164</v>
+        <v>220299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>704517</v>
+        <v>704186</v>
       </c>
       <c r="R37" t="n">
-        <v>6359895</v>
+        <v>6360035</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4598,7 +4334,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4616,10 +4352,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128305423</v>
+        <v>128305377</v>
       </c>
       <c r="B38" t="n">
-        <v>106957</v>
+        <v>110078</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4627,16 +4363,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4644,17 +4380,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>704541</v>
+        <v>704248</v>
       </c>
       <c r="R38" t="n">
-        <v>6359927</v>
+        <v>6359861</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4718,10 +4463,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128305407</v>
+        <v>128305487</v>
       </c>
       <c r="B39" t="n">
-        <v>104112</v>
+        <v>110078</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4729,34 +4474,43 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220164</v>
+        <v>220299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>704448</v>
+        <v>704285</v>
       </c>
       <c r="R39" t="n">
-        <v>6359872</v>
+        <v>6360090</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4791,6 +4545,11 @@
           <t>2025-08-11</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Pansartall, levande, med flagnande bark och en del insektshål.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4802,7 +4561,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4820,10 +4579,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128305381</v>
+        <v>128305490</v>
       </c>
       <c r="B40" t="n">
-        <v>107546</v>
+        <v>110078</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4831,43 +4590,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>704287</v>
+        <v>704264</v>
       </c>
       <c r="R40" t="n">
-        <v>6359876</v>
+        <v>6360097</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4931,10 +4681,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128305483</v>
+        <v>128305378</v>
       </c>
       <c r="B41" t="n">
-        <v>106957</v>
+        <v>107517</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4959,26 +4709,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>704298</v>
+        <v>704248</v>
       </c>
       <c r="R41" t="n">
-        <v>6360088</v>
+        <v>6359861</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5042,10 +4783,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128305490</v>
+        <v>128305385</v>
       </c>
       <c r="B42" t="n">
-        <v>109490</v>
+        <v>107517</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5053,16 +4794,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5077,10 +4818,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>704264</v>
+        <v>704296</v>
       </c>
       <c r="R42" t="n">
-        <v>6360097</v>
+        <v>6359878</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5144,10 +4885,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128305414</v>
+        <v>128305390</v>
       </c>
       <c r="B43" t="n">
-        <v>106957</v>
+        <v>107517</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5179,10 +4920,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>704517</v>
+        <v>704316</v>
       </c>
       <c r="R43" t="n">
-        <v>6359895</v>
+        <v>6359869</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5228,7 +4969,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5243,6 +4984,1428 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128305395</v>
+      </c>
+      <c r="B44" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>704369</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6359867</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128305405</v>
+      </c>
+      <c r="B45" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>704436</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6359870</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128305408</v>
+      </c>
+      <c r="B46" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>704448</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6359872</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128305411</v>
+      </c>
+      <c r="B47" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>704471</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6359883</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128305414</v>
+      </c>
+      <c r="B48" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>704517</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6359895</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128305418</v>
+      </c>
+      <c r="B49" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>704529</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6359868</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128305423</v>
+      </c>
+      <c r="B50" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>704541</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6359927</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128305475</v>
+      </c>
+      <c r="B51" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>704379</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6360148</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128305478</v>
+      </c>
+      <c r="B52" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>704346</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6360116</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128305483</v>
+      </c>
+      <c r="B53" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>704298</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6360088</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128305416</v>
+      </c>
+      <c r="B54" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>704529</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6359868</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>96223974</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lojsta Klint söder, Gtl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>704357</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6360044</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>96223975</v>
+      </c>
+      <c r="B56" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lojsta Klint söder, Gtl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>704310</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6360040</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>96223977</v>
+      </c>
+      <c r="B57" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lojsta Klint söder, Gtl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>704296</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6360103</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 569-2023 artfynd.xlsx
+++ b/artfynd/A 569-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2329,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128305384</v>
+        <v>134653588</v>
       </c>
       <c r="B19" t="n">
-        <v>99147</v>
+        <v>58460</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,46 +2340,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219864</v>
+        <v>102625</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Temminck, 1795)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+          <t>Lojsta Klint söder, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>704296</v>
+        <v>704456</v>
       </c>
       <c r="R19" t="n">
-        <v>6359878</v>
+        <v>6360062</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2403,12 +2394,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2419,78 +2420,64 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128305428</v>
+        <v>134653595</v>
       </c>
       <c r="B20" t="n">
-        <v>99147</v>
+        <v>58698</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219864</v>
+        <v>103055</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+          <t>Lojsta Klint söder, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>704514</v>
+        <v>704505</v>
       </c>
       <c r="R20" t="n">
-        <v>6360038</v>
+        <v>6360016</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2514,12 +2501,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2530,66 +2527,61 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96223970</v>
+        <v>134656132</v>
       </c>
       <c r="B21" t="n">
-        <v>108116</v>
+        <v>43290</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220079</v>
+        <v>201143</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Ängsblåvinge</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cyaniris semiargus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lojsta Klint söder, Gtl</t>
+          <t>Lojsta bjärs A 569-2023, Lojsta bjärs A 569-2023, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>704426</v>
+        <v>704402</v>
       </c>
       <c r="R21" t="n">
-        <v>6359885</v>
+        <v>6360059</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2616,12 +2608,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2636,49 +2638,49 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128305381</v>
+        <v>128305384</v>
       </c>
       <c r="B22" t="n">
-        <v>108116</v>
+        <v>99147</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2692,10 +2694,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>704287</v>
+        <v>704296</v>
       </c>
       <c r="R22" t="n">
-        <v>6359876</v>
+        <v>6359878</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2759,37 +2761,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128305392</v>
+        <v>128305428</v>
       </c>
       <c r="B23" t="n">
-        <v>108116</v>
+        <v>99147</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220079</v>
+        <v>219864</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2803,10 +2805,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>704369</v>
+        <v>704514</v>
       </c>
       <c r="R23" t="n">
-        <v>6359867</v>
+        <v>6360038</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2870,7 +2872,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128305403</v>
+        <v>96223970</v>
       </c>
       <c r="B24" t="n">
         <v>108116</v>
@@ -2898,26 +2900,17 @@
           <t>(L.) Scop.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+          <t>Lojsta Klint söder, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>704436</v>
+        <v>704426</v>
       </c>
       <c r="R24" t="n">
-        <v>6359870</v>
+        <v>6359885</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2944,12 +2937,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2960,28 +2953,23 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128305424</v>
+        <v>128305381</v>
       </c>
       <c r="B25" t="n">
         <v>108116</v>
@@ -3011,7 +2999,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3025,10 +3013,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>704541</v>
+        <v>704287</v>
       </c>
       <c r="R25" t="n">
-        <v>6359927</v>
+        <v>6359876</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3092,7 +3080,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128305426</v>
+        <v>128305392</v>
       </c>
       <c r="B26" t="n">
         <v>108116</v>
@@ -3122,7 +3110,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3136,10 +3124,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>704548</v>
+        <v>704369</v>
       </c>
       <c r="R26" t="n">
-        <v>6359959</v>
+        <v>6359867</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3203,7 +3191,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128305467</v>
+        <v>128305403</v>
       </c>
       <c r="B27" t="n">
         <v>108116</v>
@@ -3233,7 +3221,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3247,13 +3235,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>704449</v>
+        <v>704436</v>
       </c>
       <c r="R27" t="n">
-        <v>6360193</v>
+        <v>6359870</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3314,7 +3302,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128305469</v>
+        <v>128305424</v>
       </c>
       <c r="B28" t="n">
         <v>108116</v>
@@ -3344,7 +3332,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3358,10 +3346,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>704446</v>
+        <v>704541</v>
       </c>
       <c r="R28" t="n">
-        <v>6360188</v>
+        <v>6359927</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3425,10 +3413,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128305394</v>
+        <v>128305426</v>
       </c>
       <c r="B29" t="n">
-        <v>104640</v>
+        <v>108116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3436,34 +3424,43 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220164</v>
+        <v>220079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>704369</v>
+        <v>704548</v>
       </c>
       <c r="R29" t="n">
-        <v>6359867</v>
+        <v>6359959</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3527,10 +3524,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128305404</v>
+        <v>128305467</v>
       </c>
       <c r="B30" t="n">
-        <v>104640</v>
+        <v>108116</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3538,34 +3535,43 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220164</v>
+        <v>220079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>704436</v>
+        <v>704449</v>
       </c>
       <c r="R30" t="n">
-        <v>6359870</v>
+        <v>6360193</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3629,10 +3635,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128305407</v>
+        <v>128305469</v>
       </c>
       <c r="B31" t="n">
-        <v>104640</v>
+        <v>108116</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3640,34 +3646,43 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220164</v>
+        <v>220079</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>704448</v>
+        <v>704446</v>
       </c>
       <c r="R31" t="n">
-        <v>6359872</v>
+        <v>6360188</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3713,7 +3728,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3731,7 +3746,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128305410</v>
+        <v>128305394</v>
       </c>
       <c r="B32" t="n">
         <v>104640</v>
@@ -3766,10 +3781,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>704471</v>
+        <v>704369</v>
       </c>
       <c r="R32" t="n">
-        <v>6359883</v>
+        <v>6359867</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3815,7 +3830,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3833,7 +3848,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128305413</v>
+        <v>128305404</v>
       </c>
       <c r="B33" t="n">
         <v>104640</v>
@@ -3868,10 +3883,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>704517</v>
+        <v>704436</v>
       </c>
       <c r="R33" t="n">
-        <v>6359895</v>
+        <v>6359870</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3917,7 +3932,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -3935,7 +3950,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128305417</v>
+        <v>128305407</v>
       </c>
       <c r="B34" t="n">
         <v>104640</v>
@@ -3970,10 +3985,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>704529</v>
+        <v>704448</v>
       </c>
       <c r="R34" t="n">
-        <v>6359868</v>
+        <v>6359872</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4037,7 +4052,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128305421</v>
+        <v>128305410</v>
       </c>
       <c r="B35" t="n">
         <v>104640</v>
@@ -4072,10 +4087,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>704541</v>
+        <v>704471</v>
       </c>
       <c r="R35" t="n">
-        <v>6359927</v>
+        <v>6359883</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4121,7 +4136,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4139,7 +4154,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128305468</v>
+        <v>128305413</v>
       </c>
       <c r="B36" t="n">
         <v>104640</v>
@@ -4174,13 +4189,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>704446</v>
+        <v>704517</v>
       </c>
       <c r="R36" t="n">
-        <v>6360188</v>
+        <v>6359895</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4223,7 +4238,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4241,10 +4256,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128305372</v>
+        <v>128305417</v>
       </c>
       <c r="B37" t="n">
-        <v>110078</v>
+        <v>104640</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4252,43 +4267,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>704186</v>
+        <v>704529</v>
       </c>
       <c r="R37" t="n">
-        <v>6360035</v>
+        <v>6359868</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4334,7 +4340,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4352,10 +4358,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128305377</v>
+        <v>128305421</v>
       </c>
       <c r="B38" t="n">
-        <v>110078</v>
+        <v>104640</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4363,43 +4369,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>704248</v>
+        <v>704541</v>
       </c>
       <c r="R38" t="n">
-        <v>6359861</v>
+        <v>6359927</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4463,10 +4460,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128305487</v>
+        <v>128305468</v>
       </c>
       <c r="B39" t="n">
-        <v>110078</v>
+        <v>104640</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4474,46 +4471,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>704285</v>
+        <v>704446</v>
       </c>
       <c r="R39" t="n">
-        <v>6360090</v>
+        <v>6360188</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4543,11 +4531,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Pansartall, levande, med flagnande bark och en del insektshål.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4579,7 +4562,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128305490</v>
+        <v>128305372</v>
       </c>
       <c r="B40" t="n">
         <v>110078</v>
@@ -4607,17 +4590,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>704264</v>
+        <v>704186</v>
       </c>
       <c r="R40" t="n">
-        <v>6360097</v>
+        <v>6360035</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4681,10 +4673,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128305378</v>
+        <v>128305377</v>
       </c>
       <c r="B41" t="n">
-        <v>107517</v>
+        <v>110078</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4692,16 +4684,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4709,7 +4701,16 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
@@ -4783,10 +4784,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128305385</v>
+        <v>128305487</v>
       </c>
       <c r="B42" t="n">
-        <v>107517</v>
+        <v>110078</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4794,16 +4795,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4811,17 +4812,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>704296</v>
+        <v>704285</v>
       </c>
       <c r="R42" t="n">
-        <v>6359878</v>
+        <v>6360090</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4854,6 +4864,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Pansartall, levande, med flagnande bark och en del insektshål.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4885,10 +4900,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128305390</v>
+        <v>128305490</v>
       </c>
       <c r="B43" t="n">
-        <v>107517</v>
+        <v>110078</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4896,16 +4911,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4920,10 +4935,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>704316</v>
+        <v>704264</v>
       </c>
       <c r="R43" t="n">
-        <v>6359869</v>
+        <v>6360097</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4987,7 +5002,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128305395</v>
+        <v>128305378</v>
       </c>
       <c r="B44" t="n">
         <v>107517</v>
@@ -5022,10 +5037,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>704369</v>
+        <v>704248</v>
       </c>
       <c r="R44" t="n">
-        <v>6359867</v>
+        <v>6359861</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5089,7 +5104,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128305405</v>
+        <v>128305385</v>
       </c>
       <c r="B45" t="n">
         <v>107517</v>
@@ -5124,10 +5139,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>704436</v>
+        <v>704296</v>
       </c>
       <c r="R45" t="n">
-        <v>6359870</v>
+        <v>6359878</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5191,7 +5206,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128305408</v>
+        <v>128305390</v>
       </c>
       <c r="B46" t="n">
         <v>107517</v>
@@ -5226,10 +5241,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>704448</v>
+        <v>704316</v>
       </c>
       <c r="R46" t="n">
-        <v>6359872</v>
+        <v>6359869</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5275,7 +5290,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5293,7 +5308,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128305411</v>
+        <v>128305395</v>
       </c>
       <c r="B47" t="n">
         <v>107517</v>
@@ -5328,10 +5343,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>704471</v>
+        <v>704369</v>
       </c>
       <c r="R47" t="n">
-        <v>6359883</v>
+        <v>6359867</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5377,7 +5392,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5395,7 +5410,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128305414</v>
+        <v>128305405</v>
       </c>
       <c r="B48" t="n">
         <v>107517</v>
@@ -5430,10 +5445,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>704517</v>
+        <v>704436</v>
       </c>
       <c r="R48" t="n">
-        <v>6359895</v>
+        <v>6359870</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5479,7 +5494,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5497,7 +5512,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128305418</v>
+        <v>128305408</v>
       </c>
       <c r="B49" t="n">
         <v>107517</v>
@@ -5532,10 +5547,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>704529</v>
+        <v>704448</v>
       </c>
       <c r="R49" t="n">
-        <v>6359868</v>
+        <v>6359872</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5599,7 +5614,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128305423</v>
+        <v>128305411</v>
       </c>
       <c r="B50" t="n">
         <v>107517</v>
@@ -5634,10 +5649,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>704541</v>
+        <v>704471</v>
       </c>
       <c r="R50" t="n">
-        <v>6359927</v>
+        <v>6359883</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5683,7 +5698,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -5701,7 +5716,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128305475</v>
+        <v>128305414</v>
       </c>
       <c r="B51" t="n">
         <v>107517</v>
@@ -5736,10 +5751,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>704379</v>
+        <v>704517</v>
       </c>
       <c r="R51" t="n">
-        <v>6360148</v>
+        <v>6359895</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5785,7 +5800,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -5803,7 +5818,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128305478</v>
+        <v>128305418</v>
       </c>
       <c r="B52" t="n">
         <v>107517</v>
@@ -5838,10 +5853,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>704346</v>
+        <v>704529</v>
       </c>
       <c r="R52" t="n">
-        <v>6360116</v>
+        <v>6359868</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5887,7 +5902,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -5905,7 +5920,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128305483</v>
+        <v>128305423</v>
       </c>
       <c r="B53" t="n">
         <v>107517</v>
@@ -5933,26 +5948,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>704298</v>
+        <v>704541</v>
       </c>
       <c r="R53" t="n">
-        <v>6360088</v>
+        <v>6359927</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6016,10 +6022,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128305416</v>
+        <v>128305475</v>
       </c>
       <c r="B54" t="n">
-        <v>107061</v>
+        <v>107517</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6027,16 +6033,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6051,10 +6057,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>704529</v>
+        <v>704379</v>
       </c>
       <c r="R54" t="n">
-        <v>6359868</v>
+        <v>6360148</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6100,7 +6106,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6118,48 +6124,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>96223974</v>
+        <v>128305478</v>
       </c>
       <c r="B55" t="n">
-        <v>80992</v>
+        <v>107517</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>230185</v>
+        <v>221849</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lojsta Klint söder, Gtl</t>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>704357</v>
+        <v>704346</v>
       </c>
       <c r="R55" t="n">
-        <v>6360044</v>
+        <v>6360116</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6183,12 +6189,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6199,64 +6205,78 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>96223975</v>
+        <v>128305483</v>
       </c>
       <c r="B56" t="n">
-        <v>87262</v>
+        <v>107517</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>248956</v>
+        <v>221849</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lojsta Klint söder, Gtl</t>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>704310</v>
+        <v>704298</v>
       </c>
       <c r="R56" t="n">
-        <v>6360040</v>
+        <v>6360088</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6280,12 +6300,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6296,48 +6316,53 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på relikta strandvallar, nötbetad med röjda gator..</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>96223977</v>
+        <v>134653594</v>
       </c>
       <c r="B57" t="n">
-        <v>87262</v>
+        <v>107598</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>248956</v>
+        <v>221849</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6347,13 +6372,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>704296</v>
+        <v>704486</v>
       </c>
       <c r="R57" t="n">
-        <v>6360103</v>
+        <v>6360011</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6377,12 +6402,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6397,15 +6432,724 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128305416</v>
+      </c>
+      <c r="B58" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (3) A 5692-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>704529</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6359868</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på kalkflis, nötbetad med röjda gator..</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>134653597</v>
+      </c>
+      <c r="B59" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lojsta Klint söder, Gtl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>704345</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6359955</v>
+      </c>
+      <c r="S59" t="n">
+        <v>13</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>134653599</v>
+      </c>
+      <c r="B60" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lojsta Klint söder, Gtl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>704290</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6359913</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>96223974</v>
+      </c>
+      <c r="B61" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lojsta Klint söder, Gtl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>704357</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6360044</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
           <t>Helena Björnström</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
+      <c r="AX61" t="inlineStr">
         <is>
           <t>Helena Björnström</t>
         </is>
       </c>
-      <c r="AY57" t="inlineStr"/>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>96223975</v>
+      </c>
+      <c r="B62" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lojsta Klint söder, Gtl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>704310</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6360040</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>96223977</v>
+      </c>
+      <c r="B63" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lojsta Klint söder, Gtl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>704296</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6360103</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>134653598</v>
+      </c>
+      <c r="B64" t="n">
+        <v>43295</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>259083</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Eumedonia eumedon praticola</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Burrau, 1953)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lojsta Klint söder, Gtl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>704288</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6359919</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 569-2023 artfynd.xlsx
+++ b/artfynd/A 569-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AZ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -765,6 +770,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96223990</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -862,6 +872,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96223991</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -959,6 +974,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96223985</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1056,6 +1076,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96223957</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1153,6 +1178,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96223966</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1250,6 +1280,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96223953</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1347,6 +1382,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96223954</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1444,6 +1484,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96223986</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1541,6 +1586,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96223999</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1638,6 +1688,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96224000</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1735,6 +1790,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96224001</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1832,6 +1892,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96223993</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1929,6 +1994,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96223994</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2026,6 +2096,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96223995</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2123,6 +2198,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96290689</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2220,6 +2300,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96223996</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2326,6 +2411,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13185311</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2433,6 +2523,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653588</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2540,6 +2635,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653595</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2647,6 +2747,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134656132</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2758,6 +2863,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305384</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2869,6 +2979,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305428</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2966,6 +3081,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96223970</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3077,6 +3197,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305381</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3188,6 +3313,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305392</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3299,6 +3429,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305403</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3410,6 +3545,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305424</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3521,6 +3661,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305426</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3632,6 +3777,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305467</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3743,6 +3893,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305469</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3845,6 +4000,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305394</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3947,6 +4107,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305404</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4049,6 +4214,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305407</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4151,6 +4321,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305410</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4253,6 +4428,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305413</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4355,6 +4535,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305417</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4457,6 +4642,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305421</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4559,6 +4749,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305468</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4670,6 +4865,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305372</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4781,6 +4981,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305377</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4897,6 +5102,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305487</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4999,6 +5209,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305490</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5101,6 +5316,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305378</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5203,6 +5423,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305385</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5305,6 +5530,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305390</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5407,6 +5637,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305395</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5509,6 +5744,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305405</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5611,6 +5851,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305408</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5713,6 +5958,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305411</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5815,6 +6065,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305414</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5917,6 +6172,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305418</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6019,6 +6279,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305423</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6121,6 +6386,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305475</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6223,6 +6493,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305478</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6334,6 +6609,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305483</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6441,6 +6721,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653594</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6543,6 +6828,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305416</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6650,6 +6940,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653597</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6757,6 +7052,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653599</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6854,6 +7154,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96223974</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6951,6 +7256,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96223975</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7048,6 +7358,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96223977</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7150,8 +7465,78 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653598</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>